--- a/淘汰赛.xlsx
+++ b/淘汰赛.xlsx
@@ -1315,7 +1315,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>⏳ 待赛</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>⏳ 待赛</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1532,6 +1532,117 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>⏳ 待赛</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>07/12</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>挪威</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>英格兰</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>⏳ 待赛</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>07/11</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>比利时</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>⏳ 待赛</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>07/12</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>⏳ 待赛</t>
         </is>

--- a/淘汰赛.xlsx
+++ b/淘汰赛.xlsx
@@ -1104,7 +1104,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>⏳ 待赛</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>⏳ 待赛</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>
@@ -1540,22 +1540,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/12</t>
+          <t>07/11</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>挪威</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>英格兰</t>
+          <t>比利时</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1577,22 +1577,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/11</t>
+          <t>07/12</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>挪威</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>比利时</t>
+          <t>英格兰</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>瑞士</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">

--- a/淘汰赛.xlsx
+++ b/淘汰赛.xlsx
@@ -1458,9 +1458,9 @@
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>⏳ 待赛</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>⏳ 待赛</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-1【1-2】</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>⏳ 待赛</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-1【3-1】</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>⏳ 待赛</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>法国</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1748,22 +1748,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/15</t>
+          <t>07/16</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>英格兰</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">

--- a/淘汰赛.xlsx
+++ b/淘汰赛.xlsx
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>⏳ 待赛</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>⏳ 待赛</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>
@@ -1855,17 +1855,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>法国</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>英格兰</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>⏳ 待赛</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>
@@ -1952,17 +1952,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0-0【1-0】</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>⏳ 待赛</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>
